--- a/docs/package/05_Delivery/Upload_Templates/Opening_Balances_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Opening_Balances_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
   <si>
     <t xml:space="preserve">Account Code</t>
   </si>
@@ -126,10 +126,7 @@
     <t xml:space="preserve">accountName, name</t>
   </si>
   <si>
-    <t xml:space="preserve">Conditional: Debit or Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount in PHP, no sign; the account balance when it is a debit balance</t>
+    <t xml:space="preserve">Amount in PHP, no sign; the account balance when it is a debit balance. A row with no debit and no credit (zero balance) is ignored</t>
   </si>
   <si>
     <t xml:space="preserve">debit, dr</t>
@@ -180,7 +177,7 @@
     <t xml:space="preserve">Required columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Account Code (dark red headers on the Data sheet). Conditional: Debit (Debit or Credit); Credit (Debit or Credit). Other columns may be left empty or removed.</t>
+    <t xml:space="preserve">Account Code (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Header row</t>
@@ -531,16 +528,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -548,13 +545,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -573,121 +570,121 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Opening_Balances_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Opening_Balances_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
   <si>
     <t xml:space="preserve">Account Code</t>
   </si>
@@ -156,12 +156,6 @@
     <t xml:space="preserve">Accounts &gt; Period End &gt; Period Management &gt; Import opening balances</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/period-end/opening-balances/import (multipart field "file" and field goLiveDate YYYY-MM-DD)</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -171,7 +165,7 @@
     <t xml:space="preserve">Row limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Up to 20,000 data rows per file (IMPORT_MAX_ROWS) and 10 MB (IMPORT_MAX_MB).</t>
+    <t xml:space="preserve">Up to 20,000 data rows per file and 10 MB.</t>
   </si>
   <si>
     <t xml:space="preserve">Required columns</t>
@@ -192,10 +186,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -219,10 +213,10 @@
     <t xml:space="preserve">The Premiums Receivable balance should equal the total Open Balance of the Open Items upload.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -230,9 +224,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -259,8 +253,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,6 +316,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,9 +365,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -342,6 +388,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,7 +614,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -657,34 +710,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="15">
       <c r="B15" s="4" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
